--- a/data/menu.xlsx
+++ b/data/menu.xlsx
@@ -1,49 +1,209 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/barkjungha/Desktop/newdev/beginnersClass/class-list/menupan/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A4AA58-064D-1C4E-BAC6-3032AA727382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="커피" sheetId="1" r:id="rId1"/>
     <sheet name="디저트" sheetId="2" r:id="rId2"/>
     <sheet name="음료" sheetId="3" r:id="rId3"/>
     <sheet name="_설정" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="54">
+  <si>
+    <t>메뉴명</t>
+  </si>
+  <si>
+    <t>가격</t>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>품절</t>
+  </si>
+  <si>
+    <t>카테고리</t>
+  </si>
+  <si>
+    <t>아메리카노</t>
+  </si>
+  <si>
+    <t>에티오피아 싱글 오리진, 깔끔한 산미</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>에스프레소</t>
+  </si>
+  <si>
+    <t>카페라떼</t>
+  </si>
+  <si>
+    <t>부드러운 스팀 밀크와 진한 에스프레소</t>
+  </si>
+  <si>
+    <t>카푸치노</t>
+  </si>
+  <si>
+    <t>풍성한 우유 거품, 시나몬 향</t>
+  </si>
+  <si>
+    <t>바닐라 라떼</t>
+  </si>
+  <si>
+    <t>마다가스카르 바닐라 시럽</t>
+  </si>
+  <si>
+    <t>콜드브루</t>
+  </si>
+  <si>
+    <t>18시간 저온 추출, 부드러운 바디</t>
+  </si>
+  <si>
+    <t>디카페인 아메리카노</t>
+  </si>
+  <si>
+    <t>스위스 워터 디카페인 원두</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>티라미수</t>
+  </si>
+  <si>
+    <t>마스카포네 크림과 에스프레소 시럽</t>
+  </si>
+  <si>
+    <t>케이크</t>
+  </si>
+  <si>
+    <t>바스크 치즈케이크</t>
+  </si>
+  <si>
+    <t>겉은 카라멜, 속은 촉촉한 크림치즈</t>
+  </si>
+  <si>
+    <t>당근 케이크</t>
+  </si>
+  <si>
+    <t>호두와 크림치즈 프로스팅</t>
+  </si>
+  <si>
+    <t>버터 크로아상</t>
+  </si>
+  <si>
+    <t>프랑스산 버터로 구운 결 좋은 페이스트리</t>
+  </si>
+  <si>
+    <t>베이커리</t>
+  </si>
+  <si>
+    <t>아몬드 스콘</t>
+  </si>
+  <si>
+    <t>겉바속촉, 통아몬드 토핑</t>
+  </si>
+  <si>
+    <t>복숭아 아이스티</t>
+  </si>
+  <si>
+    <t>국산 복숭아 과즙, 무탄산</t>
+  </si>
+  <si>
+    <t>티</t>
+  </si>
+  <si>
+    <t>자몽 에이드</t>
+  </si>
+  <si>
+    <t>생자몽 과육이 들어간 상큼한 에이드</t>
+  </si>
+  <si>
+    <t>에이드</t>
+  </si>
+  <si>
+    <t>밀크티</t>
+  </si>
+  <si>
+    <t>아삼 홍차 베이스, 진한 풍미</t>
+  </si>
+  <si>
+    <t>딸기 라떼</t>
+  </si>
+  <si>
+    <t>생딸기 퓨레와 우유</t>
+  </si>
+  <si>
+    <t>라떼</t>
+  </si>
+  <si>
+    <t>항목</t>
+  </si>
+  <si>
+    <t>값</t>
+  </si>
+  <si>
+    <t>매장명</t>
+  </si>
+  <si>
+    <t>빌런 커피</t>
+  </si>
+  <si>
+    <t>테마</t>
+  </si>
+  <si>
+    <t>deep-green</t>
+  </si>
+  <si>
+    <t>디바이스</t>
+  </si>
+  <si>
+    <t>tablet-port</t>
+  </si>
+  <si>
+    <t>영문태그</t>
+  </si>
+  <si>
+    <t>SPECIALTY COFFEE</t>
+  </si>
+  <si>
+    <t>자동전환초</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -68,13 +228,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -399,402 +567,411 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>메뉴명</v>
-      </c>
-      <c r="B1" t="str">
-        <v>가격</v>
-      </c>
-      <c r="C1" t="str">
-        <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>품절</v>
-      </c>
-      <c r="E1" t="str">
-        <v>카테고리</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>아메리카노</v>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2">
         <v>4500</v>
       </c>
-      <c r="C2" t="str">
-        <v>에티오피아 싱글 오리진, 깔끔한 산미</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>에스프레소</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>카페라떼</v>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>9</v>
       </c>
       <c r="B3">
         <v>5000</v>
       </c>
-      <c r="C3" t="str">
-        <v>부드러운 스팀 밀크와 진한 에스프레소</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>에스프레소</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>카푸치노</v>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>11</v>
       </c>
       <c r="B4">
         <v>5000</v>
       </c>
-      <c r="C4" t="str">
-        <v>풍성한 우유 거품, 시나몬 향</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v>에스프레소</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>바닐라 라떼</v>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>13</v>
       </c>
       <c r="B5">
         <v>5500</v>
       </c>
-      <c r="C5" t="str">
-        <v>마다가스카르 바닐라 시럽</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>에스프레소</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>콜드브루</v>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>15</v>
       </c>
       <c r="B6">
-        <v>5000</v>
-      </c>
-      <c r="C6" t="str">
-        <v>18시간 저온 추출, 부드러운 바디</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v>콜드브루</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>디카페인 아메리카노</v>
+        <v>12345</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>17</v>
       </c>
       <c r="B7">
-        <v>5000</v>
-      </c>
-      <c r="C7" t="str">
-        <v>스위스 워터 디카페인 원두</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Y</v>
-      </c>
-      <c r="E7" t="str">
-        <v>에스프레소</v>
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError sqref="A1:E5 A7 A6 C6:E6 C7:E7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>메뉴명</v>
-      </c>
-      <c r="B1" t="str">
-        <v>가격</v>
-      </c>
-      <c r="C1" t="str">
-        <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>품절</v>
-      </c>
-      <c r="E1" t="str">
-        <v>카테고리</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>티라미수</v>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>20</v>
       </c>
       <c r="B2">
         <v>6500</v>
       </c>
-      <c r="C2" t="str">
-        <v>마스카포네 크림과 에스프레소 시럽</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>케이크</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>바스크 치즈케이크</v>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>23</v>
       </c>
       <c r="B3">
         <v>6800</v>
       </c>
-      <c r="C3" t="str">
-        <v>겉은 카라멜, 속은 촉촉한 크림치즈</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>케이크</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>당근 케이크</v>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>25</v>
       </c>
       <c r="B4">
         <v>6000</v>
       </c>
-      <c r="C4" t="str">
-        <v>호두와 크림치즈 프로스팅</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v>케이크</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>버터 크로아상</v>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>27</v>
       </c>
       <c r="B5">
         <v>4500</v>
       </c>
-      <c r="C5" t="str">
-        <v>프랑스산 버터로 구운 결 좋은 페이스트리</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>베이커리</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>아몬드 스콘</v>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>30</v>
       </c>
       <c r="B6">
-        <v>4000</v>
-      </c>
-      <c r="C6" t="str">
-        <v>겉바속촉, 통아몬드 토핑</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Y</v>
-      </c>
-      <c r="E6" t="str">
-        <v>베이커리</v>
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError sqref="A1:E5 A6 C6:E6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>메뉴명</v>
-      </c>
-      <c r="B1" t="str">
-        <v>가격</v>
-      </c>
-      <c r="C1" t="str">
-        <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>품절</v>
-      </c>
-      <c r="E1" t="str">
-        <v>카테고리</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>복숭아 아이스티</v>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>32</v>
       </c>
       <c r="B2">
         <v>5000</v>
       </c>
-      <c r="C2" t="str">
-        <v>국산 복숭아 과즙, 무탄산</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>티</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>자몽 에이드</v>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>35</v>
       </c>
       <c r="B3">
         <v>5800</v>
       </c>
-      <c r="C3" t="str">
-        <v>생자몽 과육이 들어간 상큼한 에이드</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>에이드</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>밀크티</v>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>38</v>
       </c>
       <c r="B4">
         <v>5500</v>
       </c>
-      <c r="C4" t="str">
-        <v>아삼 홍차 베이스, 진한 풍미</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v>티</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>딸기 라떼</v>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>6000</v>
-      </c>
-      <c r="C5" t="str">
-        <v>생딸기 퓨레와 우유</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>라떼</v>
+        <v>123</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError sqref="A1:E4 A5 C5:E5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>항목</v>
-      </c>
-      <c r="B1" t="str">
-        <v>값</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>매장명</v>
-      </c>
-      <c r="B2" t="str">
-        <v>빌런 커피</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>테마</v>
-      </c>
-      <c r="B3" t="str">
-        <v>deep-green</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>디바이스</v>
-      </c>
-      <c r="B4" t="str">
-        <v>tablet-port</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>영문태그</v>
-      </c>
-      <c r="B5" t="str">
-        <v>SPECIALTY COFFEE</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>자동전환초</v>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>53</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError sqref="A1:B6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/menu.xlsx
+++ b/data/menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/barkjungha/Desktop/newdev/beginnersClass/class-list/menupan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A4AA58-064D-1C4E-BAC6-3032AA727382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B43F194-710D-3F4B-BD96-113918CEE6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="28200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="커피" sheetId="1" r:id="rId1"/>
@@ -169,9 +169,6 @@
     <t>테마</t>
   </si>
   <si>
-    <t>deep-green</t>
-  </si>
-  <si>
     <t>디바이스</t>
   </si>
   <si>
@@ -185,6 +182,10 @@
   </si>
   <si>
     <t>자동전환초</t>
+  </si>
+  <si>
+    <t>cream</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -940,28 +941,28 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
         <v>49</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
         <v>51</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -971,7 +972,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B2 A4:B6 A3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>